--- a/serverFireStation/fire_station_project/report_templates/fire_truck.xlsx
+++ b/serverFireStation/fire_station_project/report_templates/fire_truck.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\server\serverFireStation\fire_station_project\report_templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Дмитрий\Desktop\Diplom_Application\FFGSM\serverFireStation\fire_station_project\report_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EF3850-61C7-40E4-95E6-0FC8F81E71B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DFEA45-64BD-4799-BA32-85C352925111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -119,41 +119,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
       <sz val="8"/>
@@ -239,113 +211,83 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -627,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -649,269 +591,254 @@
     <col min="19" max="19" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
     </row>
-    <row r="2" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="22" t="s">
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
     </row>
-    <row r="3" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+    <row r="3" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="U3" s="24"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="5"/>
+      <c r="U3" s="10"/>
     </row>
-    <row r="4" spans="1:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+    <row r="4" spans="1:21" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="26"/>
-      <c r="K4" s="29" t="s">
+      <c r="J4" s="13"/>
+      <c r="K4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="29"/>
-      <c r="M4" s="25" t="s">
+      <c r="L4" s="11"/>
+      <c r="M4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="25"/>
-      <c r="O4" s="18" t="s">
+      <c r="N4" s="9"/>
+      <c r="O4" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="P4" s="25" t="s">
+      <c r="P4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="Q4" s="19" t="s">
+      <c r="Q4" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="R4" s="20" t="s">
+      <c r="R4" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="S4" s="21" t="s">
+      <c r="S4" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="T4" s="27" t="s">
+      <c r="T4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="U4" s="27" t="s">
+      <c r="U4" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="V4" s="7"/>
-      <c r="W4" s="3"/>
     </row>
-    <row r="5" spans="1:25" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="10" t="s">
+    <row r="5" spans="1:21" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="17" t="s">
+      <c r="K5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="17" t="s">
+      <c r="L5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="M5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="18"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="21"/>
-      <c r="T5" s="27"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="4"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>1</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="4">
         <v>3</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="3">
         <v>4</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="3">
         <v>5</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="4">
         <v>6</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="3">
         <v>7</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="5">
         <v>8</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="3">
         <v>9</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="5">
         <v>10</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="5">
         <v>11</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="5">
         <v>12</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="4">
         <v>13</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="4">
         <v>14</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6" s="6">
         <v>15</v>
       </c>
-      <c r="P6" s="13">
+      <c r="P6" s="4">
         <v>16</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="Q6" s="4">
         <v>17</v>
       </c>
-      <c r="R6" s="15">
+      <c r="R6" s="6">
         <v>18</v>
       </c>
-      <c r="S6" s="16">
+      <c r="S6" s="7">
         <v>19</v>
       </c>
-      <c r="T6" s="12">
+      <c r="T6" s="3">
         <v>20</v>
       </c>
-      <c r="U6" s="12">
+      <c r="U6" s="3">
         <v>21</v>
       </c>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:U2"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="A4:A5"/>
@@ -928,12 +855,11 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="T3:U3"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:U2"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="landscape" r:id="rId1"/>
